--- a/spreadsheet/TMHカレンダーインポートツール.xlsx
+++ b/spreadsheet/TMHカレンダーインポートツール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\tmh-calendar-import-tool\spreadsheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A63A38A-B359-4C5F-BBF1-0748EB5D518D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198D9FF2-AB7B-4FB4-AAA4-15B24CE5C154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TMHカレンダーインポートツール" sheetId="2" r:id="rId1"/>
@@ -21,20 +21,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>概要</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
+    <t>モード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ドキュメントURL</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>本ファイルは、</t>
+      <t>本シートは、</t>
     </r>
     <r>
       <rPr>
@@ -50,29 +61,428 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
+        <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>カレンダーをインポート</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
+      <t>スケジュールを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Google </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>するためのツールです。</t>
-    </r>
-    <phoneticPr fontId="3"/>
+      <t>カレンダーへ取り込むための操作パネルです。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「モード」と「ドキュメント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」を設定し、「インポートの開始」から実行してください。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>処理の記録は「ログ」シートを確認してください。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>【モードに指定する値】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+all … </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>全て（フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>：ドキュメント作成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>：カレンダー登録</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>：完了フォルダへ移動）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+createDocumentsOnly … </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>のみ（ドキュメント作成。ログのファイル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を確認）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+importOnly … </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>のみ（カレンダー登録。「ドキュメント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」の指定が必要）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+moveOnly … </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>のみ（インポート対象ファイルを完了フォルダへ移動）</t>
+    </r>
+    <rPh sb="133" eb="134">
+      <t>スベ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -80,14 +490,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
@@ -95,20 +500,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
@@ -123,6 +514,35 @@
       <name val="Arial"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -132,7 +552,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -142,53 +562,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -196,12 +579,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -501,25 +898,45 @@
   <dimension ref="A1:F981"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.36328125" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="6" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="167.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1499,10 +1916,17 @@
     <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:F2" xr:uid="{9C0B92A6-3D59-48EE-82B2-30ACFCDEC264}">
+      <formula1>"all,createDocumentsOnly,importOnly,moveOnly"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2520,7 +2944,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>